--- a/tools/generate-testdoc/templates/test_spec_template.xlsx
+++ b/tools/generate-testdoc/templates/test_spec_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\testcase\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\prompt-cookbook\tools\generate-testdoc\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA93B0A-8680-4845-8AE6-7258FD748001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4789BE3F-5AFE-488D-90FE-F797F3CD34EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト観点" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>作成者：</t>
-  </si>
-  <si>
-    <t>張</t>
   </si>
   <si>
     <t>kintoneレコード：</t>
@@ -651,9 +648,7 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="4"/>
@@ -661,7 +656,7 @@
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="7"/>
@@ -692,7 +687,7 @@
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
@@ -723,19 +718,19 @@
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>7</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>8</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
@@ -984,7 +979,7 @@
     <row r="1" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17"/>
       <c r="B1" s="18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="19">
         <f>($C$3+$C$6)/$C$2</f>
@@ -1001,7 +996,7 @@
     <row r="2" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20"/>
       <c r="B2" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="21">
         <f>COUNT($A$9:$A$122)</f>
@@ -1017,7 +1012,7 @@
     <row r="3" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20"/>
       <c r="B3" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="21">
         <f>COUNTIF($F$9:$F$123,"OK")</f>
@@ -1033,7 +1028,7 @@
     <row r="4" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20"/>
       <c r="B4" s="18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="21">
         <f>COUNTIF($F$9:$F$123,"NG")</f>
@@ -1049,7 +1044,7 @@
     <row r="5" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A5" s="20"/>
       <c r="B5" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="21">
         <f>COUNTIF($F$9:$F$123,"保留")</f>
@@ -1065,7 +1060,7 @@
     <row r="6" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A6" s="20"/>
       <c r="B6" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="21">
         <f>COUNTIF($F$9:$F$123,"対象外")</f>
@@ -1081,7 +1076,7 @@
     <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A7" s="20"/>
       <c r="B7" s="28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="29">
         <f>C2-(C3+C4+C5)</f>
@@ -1096,31 +1091,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="30" t="s">
+      <c r="D8" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="E8" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="F8" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="G8" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="H8" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="30" t="s">
-        <v>22</v>
-      </c>
       <c r="I8" s="30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2721,28 +2716,28 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C123" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D123" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E123" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F123" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G123" s="23"/>
       <c r="H123" s="23"/>
       <c r="I123" s="23"/>
       <c r="J123" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2772,13 +2767,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="25"/>
     </row>
@@ -3810,14 +3805,14 @@
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B116" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C116" s="27"/>
       <c r="D116" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
